--- a/public/coffee/kitchen.xlsx
+++ b/public/coffee/kitchen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elizaveta/Desktop/projects/sage/GkirillS.github.io/public/coffee/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D06A05-5395-204B-AB70-592CA93796FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE93203-C6EB-3B47-9EBA-7B6818F13CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="catalogs" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="88">
   <si>
     <t>name_ru</t>
   </si>
@@ -175,21 +175,6 @@
     <t>The dish is cooked in a fragrant tomato sauce with bell pepper, spices and sesame tahini sauce, topped with a poached egg, served with crusty bread</t>
   </si>
   <si>
-    <t>Французские тосты с вишней и мороженым</t>
-  </si>
-  <si>
-    <t>French toast with cherries and ice cream</t>
-  </si>
-  <si>
-    <t>ფრანგული სადღეგრძელო ალუბლითა და ნაყინით</t>
-  </si>
-  <si>
-    <t>Нежные тосты из обжаренного хлеба, пропитанного сладкой яичной смесью, подаются с кисло-сладким вишневым соусом и шариком ванильного мороженого</t>
-  </si>
-  <si>
-    <t>Delicate toasts of toasted bread soaked in sweet egg mixture served with sweet and sour cherry sauce and a scoop of vanilla ice cream</t>
-  </si>
-  <si>
     <t>Творожные сырники со сметаной и вишневым компоте</t>
   </si>
   <si>
@@ -247,30 +232,6 @@
     <t>ხრაშუნა პური სურნელოვანი
 კარაქი, კრემისებრი ყველის ნარევების ქვეშ, რომელსაც ავსებს ცხარე სალსა, სურნელოვანი მწვანილი,
 მსუბუქად დამარილებული ორაგულითა და ანჩოუს ზეთით</t>
-  </si>
-  <si>
-    <t>Бранчпури с пепперони, чесночным маслом и травами</t>
-  </si>
-  <si>
-    <t>Brunchpuri with pepperoni, garlic butter and herbes</t>
-  </si>
-  <si>
-    <t>ბრუნჩპური პეპერონით, ნივრის კარაქით და მწვანილებით</t>
-  </si>
-  <si>
-    <t>Хрустящий хлеб с ароматным
-маслом, под сливочно-сырным скремблом, дополненный пикантной сальсой, ароматными травами, 
-с пепперони  и чесночным маслом</t>
-  </si>
-  <si>
-    <t>Crispy bread with fragrant
-butter, under a creamy cheese scramble, complemented with spicy salsa, aromatic herbs,
-pepperoni and garlic butter</t>
-  </si>
-  <si>
-    <t>ხრაშუნა პური სურნელოვანი
-კარაქი, კრემისებრი ყველის ნარევების ქვეშ, დამატებული ცხარე სალსით, არომატული მწვანილებით,
-პეპერონი და ნიორი კარაქი</t>
   </si>
   <si>
     <t>Бранчпури с копченой курицей, чесночным маслом и травами</t>
@@ -752,7 +713,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AD1009"/>
+  <dimension ref="A1:AD1008"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="7" max="7" width="65.33203125" customWidth="1"/>
@@ -803,7 +764,7 @@
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="7" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>25</v>
@@ -815,11 +776,11 @@
         <v>27</v>
       </c>
       <c r="I2" s="2" t="str">
-        <f t="shared" ref="I2:I12" si="0">LOWER($B2)</f>
+        <f t="shared" ref="I2:I11" si="0">LOWER($B2)</f>
         <v>oatmeal porridge with smoked chiken and pesto sause</v>
       </c>
       <c r="J2" s="2" t="str">
-        <f t="shared" ref="J2:J9" si="1">LOWER($B2)&amp;"_"&amp;2</f>
+        <f t="shared" ref="J2:J8" si="1">LOWER($B2)&amp;"_"&amp;2</f>
         <v>oatmeal porridge with smoked chiken and pesto sause_2</v>
       </c>
     </row>
@@ -944,96 +905,97 @@
         <v>46</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>47</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>48</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>50</v>
-      </c>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>french toast with cherries and ice cream</v>
+        <v>syrniki with sour cream and cherries</v>
       </c>
       <c r="J7" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>french toast with cherries and ice cream_2</v>
+        <v>syrniki with sour cream and cherries_2</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="13">
-      <c r="A8" s="8" t="s">
-        <v>51</v>
+      <c r="A8" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>52</v>
+      <c r="C8" s="5" t="s">
+        <v>50</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10">
-        <v>18</v>
+      <c r="E8" s="5">
+        <v>19</v>
       </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="2"/>
       <c r="I8" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>syrniki with sour cream and cherries</v>
+        <v>bruschetta with salmon</v>
       </c>
       <c r="J8" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>syrniki with sour cream and cherries_2</v>
+        <v>bruschetta with salmon_2</v>
       </c>
     </row>
-    <row r="9" spans="1:30" ht="13">
-      <c r="A9" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" s="5">
-        <v>19</v>
-      </c>
+    <row r="9" spans="1:30" ht="15">
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="7"/>
       <c r="I9" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>bruschetta with salmon</v>
+        <v/>
       </c>
-      <c r="J9" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>bruschetta with salmon_2</v>
-      </c>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="2"/>
+      <c r="Z9" s="2"/>
+      <c r="AA9" s="2"/>
+      <c r="AB9" s="2"/>
+      <c r="AC9" s="2"/>
+      <c r="AD9" s="2"/>
     </row>
     <row r="10" spans="1:30" ht="15">
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
       <c r="H10" s="7"/>
       <c r="I10" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
@@ -1063,8 +1025,8 @@
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
@@ -1084,10 +1046,7 @@
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
       <c r="H12" s="7"/>
-      <c r="I12" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="I12" s="7"/>
       <c r="J12" s="2"/>
       <c r="K12" s="9"/>
       <c r="L12" s="2"/>
@@ -1166,14 +1125,14 @@
       <c r="AC14" s="2"/>
       <c r="AD14" s="2"/>
     </row>
-    <row r="15" spans="1:30" ht="15">
+    <row r="15" spans="1:30" ht="13">
       <c r="E15" s="2"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
       <c r="J15" s="2"/>
-      <c r="K15" s="9"/>
+      <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -28998,34 +28957,6 @@
       <c r="AC1008" s="2"/>
       <c r="AD1008" s="2"/>
     </row>
-    <row r="1009" spans="5:30" ht="13">
-      <c r="E1009" s="2"/>
-      <c r="F1009" s="2"/>
-      <c r="G1009" s="2"/>
-      <c r="H1009" s="13"/>
-      <c r="I1009" s="13"/>
-      <c r="J1009" s="2"/>
-      <c r="K1009" s="2"/>
-      <c r="L1009" s="2"/>
-      <c r="M1009" s="2"/>
-      <c r="N1009" s="2"/>
-      <c r="O1009" s="2"/>
-      <c r="P1009" s="2"/>
-      <c r="Q1009" s="2"/>
-      <c r="R1009" s="2"/>
-      <c r="S1009" s="2"/>
-      <c r="T1009" s="2"/>
-      <c r="U1009" s="2"/>
-      <c r="V1009" s="2"/>
-      <c r="W1009" s="2"/>
-      <c r="X1009" s="2"/>
-      <c r="Y1009" s="2"/>
-      <c r="Z1009" s="2"/>
-      <c r="AA1009" s="2"/>
-      <c r="AB1009" s="2"/>
-      <c r="AC1009" s="2"/>
-      <c r="AD1009" s="2"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -29036,7 +28967,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="7" max="7" width="67.6640625" customWidth="1"/>
@@ -29076,57 +29007,57 @@
     </row>
     <row r="2" spans="1:10" ht="15">
       <c r="A2" s="8" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="7" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I2" s="2" t="str">
-        <f t="shared" ref="I2:I5" si="0">LOWER($B2)</f>
+        <f t="shared" ref="I2:I4" si="0">LOWER($B2)</f>
         <v>brunchpuri with shrimp and anchovy butter</v>
       </c>
       <c r="J2" s="2" t="str">
-        <f t="shared" ref="J2:J5" si="1">LOWER($B2)&amp;"_"&amp;2</f>
+        <f t="shared" ref="J2:J4" si="1">LOWER($B2)&amp;"_"&amp;2</f>
         <v>brunchpuri with shrimp and anchovy butter_2</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E3" s="5">
         <v>20</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="I3" s="2" t="str">
         <f t="shared" si="0"/>
@@ -29138,77 +29069,46 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A4" s="8" t="s">
-        <v>68</v>
+      <c r="A4" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E4" s="5">
         <v>18</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>72</v>
+      <c r="G4" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I4" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>brunchpuri with pepperoni, garlic butter and herbes</v>
+        <v>brunchpuri with chicken, garlic butter and herbes</v>
       </c>
       <c r="J4" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>brunchpuri with pepperoni, garlic butter and herbes_2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A5" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="5">
-        <v>18</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I5" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>brunchpuri with chicken, garlic butter and herbes</v>
-      </c>
-      <c r="J5" s="2" t="str">
-        <f t="shared" si="1"/>
         <v>brunchpuri with chicken, garlic butter and herbes_2</v>
       </c>
     </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
+      <c r="B5" s="8"/>
+      <c r="C5" s="2"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+    </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1">
-      <c r="B6" s="8"/>
-      <c r="C6" s="2"/>
       <c r="G6" s="8"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-    </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1">
-      <c r="G7" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -29262,23 +29162,23 @@
     </row>
     <row r="2" spans="1:10" ht="15">
       <c r="A2" s="8" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="14" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="str">
@@ -29292,22 +29192,22 @@
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E3" s="5">
         <v>21</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="str">
@@ -29321,22 +29221,22 @@
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="E4" s="5">
         <v>20</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I4" s="2" t="str">
         <f t="shared" si="0"/>

--- a/public/coffee/kitchen.xlsx
+++ b/public/coffee/kitchen.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elizaveta/Desktop/projects/sage/GkirillS.github.io/public/coffee/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE93203-C6EB-3B47-9EBA-7B6818F13CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F946A859-D5F2-454C-8B88-B8C974CEF007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="12400" windowHeight="16260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="catalogs" sheetId="1" r:id="rId1"/>
     <sheet name="breakfast" sheetId="2" r:id="rId2"/>
     <sheet name="branchpuri" sheetId="3" r:id="rId3"/>
-    <sheet name="bowl" sheetId="4" r:id="rId4"/>
+    <sheet name="pancakes" sheetId="5" r:id="rId4"/>
+    <sheet name="bowl" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="101">
   <si>
     <t>name_ru</t>
   </si>
@@ -314,12 +315,51 @@
   <si>
     <t>14</t>
   </si>
+  <si>
+    <t>Блины</t>
+  </si>
+  <si>
+    <t>Pancakes</t>
+  </si>
+  <si>
+    <t>Блин чизбургер</t>
+  </si>
+  <si>
+    <t>Pancakes cheeseburger</t>
+  </si>
+  <si>
+    <t>პანკეიქების ჩიზბურგერი</t>
+  </si>
+  <si>
+    <t>Блины с лососем, крем чизом и огурцом</t>
+  </si>
+  <si>
+    <t>Pancakes with salmon, cream cheese and cucumber</t>
+  </si>
+  <si>
+    <t>ბლინები ლოსოსით, კრემ-ჩიზით და კიტრით</t>
+  </si>
+  <si>
+    <t>Блины со сгущенкой и бананом</t>
+  </si>
+  <si>
+    <t>Pancakes with condensed milk and banana</t>
+  </si>
+  <si>
+    <t>ბლინები შესქელებული რძით და ბანანით</t>
+  </si>
+  <si>
+    <t>shakshuka1</t>
+  </si>
+  <si>
+    <t>shakshuka1_2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="15">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -390,6 +430,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -417,7 +481,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -435,6 +499,10 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -653,7 +721,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.33203125" customWidth="1"/>
@@ -693,13 +761,24 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -891,13 +970,11 @@
         <v>45</v>
       </c>
       <c r="H6" s="2"/>
-      <c r="I6" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>shakshuka</v>
+      <c r="I6" s="10" t="s">
+        <v>99</v>
       </c>
-      <c r="J6" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>shakshuka_2</v>
+      <c r="J6" s="10" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="13">
@@ -29116,6 +29193,140 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A90C241-B2A6-3E44-91E2-8D012567708D}">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col min="7" max="7" width="67.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15">
+      <c r="A1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="19">
+      <c r="A2" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15">
+        <v>18</v>
+      </c>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2" t="str">
+        <f t="shared" ref="I2:I4" si="0">LOWER($B2)</f>
+        <v>pancakes cheeseburger</v>
+      </c>
+      <c r="J2" s="2" t="str">
+        <f t="shared" ref="J2:J4" si="1">LOWER($B2)&amp;"_"&amp;2</f>
+        <v>pancakes cheeseburger_2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A3" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15">
+        <v>18</v>
+      </c>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pancakes with salmon, cream cheese and cucumber</v>
+      </c>
+      <c r="J3" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>pancakes with salmon, cream cheese and cucumber_2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A4" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15">
+        <v>14</v>
+      </c>
+      <c r="F4" s="8"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pancakes with condensed milk and banana</v>
+      </c>
+      <c r="J4" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>pancakes with condensed milk and banana_2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
+      <c r="B5" s="8"/>
+      <c r="C5" s="2"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
+      <c r="G6" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
